--- a/excel/Prominence_Sensitivity.xlsx
+++ b/excel/Prominence_Sensitivity.xlsx
@@ -726,7 +726,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Source: supplement/prominence_sensitivity/ (prominence_sensitivity.py, summarize.py, partials/).</t>
+          <t>Source: reproduction/prominence_sensitivity/ (prominence_sensitivity.py, summarize.py, partials/).</t>
         </is>
       </c>
     </row>
